--- a/tests/fixtures/row_formats/planted.xlsx
+++ b/tests/fixtures/row_formats/planted.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp2ob04_j6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp8pn_8tbf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B17C2AA1-DECA-4A29-A9BB-91EC8BAA23B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51677D8-073A-4CC7-AB8D-3CFACA5D8C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="19440" windowHeight="11220" firstSheet="16" activeTab="16" xr2:uid="{3006D08A-CC30-403A-9A09-34E6E7F13B5B}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="7920" windowHeight="13995" firstSheet="16" activeTab="16" xr2:uid="{7D6F9D99-0274-459F-8DBA-A6A36762ED2A}"/>
   </bookViews>
   <sheets>
     <sheet name="styles" sheetId="1" r:id="rId1"/>
@@ -468,7 +468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A51A10-EE92-4D41-8862-85566536AEDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F5D793-9CB0-42A4-BE1D-4F4B74A15EB0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -484,7 +484,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE2DC8B-FDF0-4974-A3E8-02C69D9D32B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D998A8-EC88-4A01-8308-29BFF2084A86}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EEB0ED-3252-4310-8BB7-972CC51490D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{072F3444-AB48-4D1C-93CF-BF86C60F1D4E}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -510,7 +510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A8902C-0C27-4D23-B1E0-7AD0E0460C81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B460CD-A9C5-49B7-8A3D-2E453B08F5B0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -519,7 +519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EA6791-7DE2-41FD-8F83-5244F690763A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAD5FA1-84D1-4035-B288-F83C19FB92ED}">
   <dimension ref="C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -532,7 +532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CDE9351-EBEC-49BC-91A8-24AB83B9FF8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B2138F-6FB8-4398-A3FA-F0D90AADEC91}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BB1EB1-7178-43A5-9897-5F6997307AF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A02EA45C-A655-42A7-8B84-7156E0B749C6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -552,7 +552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85FBFC3-BDC0-4C96-AB51-D7F076079B2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED3A022D-5A09-472C-9B85-26D55451A666}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF424D55-D50C-4028-AB76-6976620ED430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAA1AE0-AE6C-454D-A825-C92F75435E60}">
   <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -575,7 +575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4626528E-F755-4BBB-BBED-14252D690978}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC8BBDE-D3B8-4C89-8370-8653E87AB8F8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -587,7 +587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B1DC9F-DB40-46A5-B499-2CEDB5E3C145}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA67A34C-7375-4686-BD33-4D3066EA7684}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -601,7 +601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3A52E4-7493-4058-B403-CA35E6369C01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA91E23-C9D4-4EEC-9F1B-0A4D7403629B}">
   <dimension ref="A1:XFC1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -614,7 +614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711ACC96-51EB-42C4-8553-353012FC9F0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D68926-E4E6-42BA-8C44-EDCE2AE0123A}">
   <dimension ref="A1:LCB1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8525410E-0AC5-4FCD-B131-7A2702191429}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9335329-0707-4D20-A1DF-D6BCBA76C77B}">
   <dimension ref="A1:XFC1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -639,7 +639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F88B1FB-4A3E-48CE-A262-746B67B2A1F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11553EF-044A-455B-9D5B-BFDDC3D9F1CF}">
   <dimension ref="A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -653,7 +653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AB0128-19A1-4F75-B759-933337539324}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7486D8D2-3EB4-46B4-B703-F54BECEBBBA6}">
   <dimension ref="C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -671,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97603FD8-3E17-4CDD-A908-930ADDE6E15A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC9A50A-AA2F-4B33-A033-345A26117BD3}">
   <dimension ref="C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/tests/fixtures/row_formats/planted.xlsx
+++ b/tests/fixtures/row_formats/planted.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmp8pn_8tbf\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{E51677D8-073A-4CC7-AB8D-3CFACA5D8C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="7920" windowHeight="13995" firstSheet="16" activeTab="16" xr2:uid="{7D6F9D99-0274-459F-8DBA-A6A36762ED2A}"/>
